--- a/Conditional Formatting Excel Tutorial File.xlsx
+++ b/Conditional Formatting Excel Tutorial File.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/579481080490e445/Documents/Excel Series Excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/62e96a89a7a77bdd/Desktop/Excel_Learn/Learn_Excel_By_Alex_the_Analyst/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE12AABD-2C2A-4D60-B298-E861FD33474F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{EE12AABD-2C2A-4D60-B298-E861FD33474F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4270C635-18C3-4635-A57D-82FDA8F74067}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" r:id="rId1"/>
     <sheet name="Sales" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="85">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -1198,4 +1199,184 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E41DAE2-E4D1-4D87-8650-BDABCC48F3D6}">
+  <dimension ref="A2:M5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3">
+        <v>450</v>
+      </c>
+      <c r="C3">
+        <v>310</v>
+      </c>
+      <c r="D3">
+        <v>150</v>
+      </c>
+      <c r="E3">
+        <v>750</v>
+      </c>
+      <c r="F3">
+        <v>440</v>
+      </c>
+      <c r="G3">
+        <v>485</v>
+      </c>
+      <c r="H3">
+        <v>510</v>
+      </c>
+      <c r="I3">
+        <v>347</v>
+      </c>
+      <c r="J3">
+        <v>736</v>
+      </c>
+      <c r="K3">
+        <v>155</v>
+      </c>
+      <c r="L3">
+        <v>450</v>
+      </c>
+      <c r="M3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>65</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4">
+        <v>24</v>
+      </c>
+      <c r="G4">
+        <v>71</v>
+      </c>
+      <c r="H4">
+        <v>57</v>
+      </c>
+      <c r="I4">
+        <v>61</v>
+      </c>
+      <c r="J4">
+        <v>34</v>
+      </c>
+      <c r="K4">
+        <v>41</v>
+      </c>
+      <c r="L4">
+        <v>58</v>
+      </c>
+      <c r="M4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5">
+        <v>200</v>
+      </c>
+      <c r="C5">
+        <v>118</v>
+      </c>
+      <c r="D5">
+        <v>145</v>
+      </c>
+      <c r="E5">
+        <v>210</v>
+      </c>
+      <c r="F5">
+        <v>45</v>
+      </c>
+      <c r="G5">
+        <v>170</v>
+      </c>
+      <c r="H5">
+        <v>130</v>
+      </c>
+      <c r="I5">
+        <v>90</v>
+      </c>
+      <c r="J5">
+        <v>55</v>
+      </c>
+      <c r="K5">
+        <v>110</v>
+      </c>
+      <c r="L5">
+        <v>130</v>
+      </c>
+      <c r="M5">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A3:M5">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>